--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:28</t>
+    <t xml:space="preserve">2026-09-10 01:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:43</t>
+    <t xml:space="preserve">2026-09-18 11:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:39</t>
+    <t xml:space="preserve">2026-09-23 15:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2024_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2024_metropolitana.xlsx
@@ -210,7 +210,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:45</t>
+    <t xml:space="preserve">2026-10-05 17:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1303,7 +1303,7 @@
         <v>95.81</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>107.36</v>
+        <v>107.37</v>
       </c>
     </row>
     <row r="25">
